--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.7799778046745</v>
+        <v>4.839246393259606</v>
       </c>
       <c r="D2" t="n">
-        <v>29.27931779594472</v>
+        <v>4.757889141841017</v>
       </c>
       <c r="E2" t="n">
-        <v>6.492626752212145</v>
+        <v>1.055051847234473</v>
       </c>
       <c r="F2" t="n">
-        <v>6.468631356692514</v>
+        <v>1.051152595462534</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.79472430025021</v>
+        <v>2.72914269879066</v>
       </c>
       <c r="D3" t="n">
-        <v>16.34205508255969</v>
+        <v>2.65558395091595</v>
       </c>
       <c r="E3" t="n">
-        <v>6.492626752212145</v>
+        <v>1.055051847234473</v>
       </c>
       <c r="F3" t="n">
-        <v>6.468631356692514</v>
+        <v>1.051152595462534</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
